--- a/public/examples/france-south-loop.xlsx
+++ b/public/examples/france-south-loop.xlsx
@@ -11,257 +11,6 @@
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A4" authorId="0">
-      <text>
-        <r>
-          <t>Required · YYYY-MM-DD</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · HH:MM (24h)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · HH:MM (24h)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D4" authorId="0">
-      <text>
-        <r>
-          <t>Required · flight, train, bus, ferry, drive, sight, restaurant, activity, city, note, other</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E4" authorId="0">
-      <text>
-        <r>
-          <t>Required · free text</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · free text</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · free text</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · place or IATA</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · place or IATA</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · booking ref</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · number ≥ 0</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · 3-letter code (EUR)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · planned / booked / done / cancelled</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · free text</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · https://…</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · comma-separated</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · decimal degrees</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="R4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · decimal degrees</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · decimal degrees</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · decimal degrees</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A4" authorId="0">
-      <text>
-        <r>
-          <t>Required · YYYY-MM-DD</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B4" authorId="0">
-      <text>
-        <r>
-          <t>Preferred · YYYY-MM-DD (defaults to check-in)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C4" authorId="0">
-      <text>
-        <r>
-          <t>Required · free text</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · free text</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · free text</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · booking ref</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · number ≥ 0</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · 3-letter code (EUR)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · planned / booked / done / cancelled</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · free text</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · https://…</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · decimal degrees</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M4" authorId="0">
-      <text>
-        <r>
-          <t>Optional · decimal degrees</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4620,9 +4369,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5042,9 +4790,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
